--- a/plugins/redmineflux_crux_qa/automation/testdata/CRUX_TESTDATA_LOCAL.xlsx
+++ b/plugins/redmineflux_crux_qa/automation/testdata/CRUX_TESTDATA_LOCAL.xlsx
@@ -17,6 +17,10 @@
     <sheet name="CRM Deals (test)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Work Packages (test)" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Frozen Rules (test)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Workload (test)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Budget Audit (test)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Agile Board (test)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Knowledge Base (test)" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -814,6 +818,727 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name / ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Purpose / Used By (TC)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Last Verified</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>#1 Platform Engineering</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deleted</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TC-CRX-096 (create/member/skill), TC-CRX-100 (delete)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Created via chat 2026-09-16, members luna.blossom/daisy.skye added then bulk-removed (TC-096), deleted via chat (TC-100). /rf_teams confirmed back to 'No teams have been created yet.' afterward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>#1 Kubernetes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Active (team deleted, skill orphaned)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TC-CRX-096 (skill create + assign)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Created via chat, assigned to luna.blossom (user 5) in Platform Engineering team. Team since deleted (TC-100) — skill record itself not re-checked after that deletion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Workload</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>#1 Platform Engineering Sprint 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Active, 0h planned</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TC-CRX-094 (allocation writes — FAIL, see BUG-CRX-018)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Created via chat, 2026-09-16 to 2026-10-16, 8h/day. Issue #9 added (workload_issue_id: 1) but resize/update-dates both failed (BUG-CRX-018) — remains at 0.0h planned. Left in place, not cleaned up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Issue (fixture)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>#9 TC-CRX-094 Allocation Write Test Issue</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New, assigned to Redmine Admin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TC-CRX-094 (allocation writes)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Created via New Issue form (Crux QA project) specifically because issue #8 could not be assigned to Redmine Admin (Admin not a project member with an assignable role — membership-add attempt silently failed, not investigated further). Added to Workload #1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Holiday Scheme</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>#1 US Federal Holidays 2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Active, 1 holiday</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TC-CRX-097 (holiday scheme lifecycle)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Created via chat, holiday 'Christmas Day' (2026-12-25) added, then activated. Left in place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Holiday Scheme</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>#2 US Federal Holidays 2026 Copy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Inactive (clone), 1 holiday</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TC-CRX-097 (holiday scheme clone)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cloned from Scheme #1 via chat — verified inactive-by-default and holiday duplicated correctly on the real /rf_settings page. Left in place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>#1 luna.blossom (user 5), Planned, 2026-09-21 to 2026-09-23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TC-CRX-095 (leave lifecycle — create/approve)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Created then approved via chat. Verified on real /rf_leaves Team Approvals tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>#2 luna.blossom (user 5), Sick, 2026-10-01 to 2026-10-02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TC-CRX-095 (leave lifecycle — create/reject), BUG-CRX-019</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>First create attempt (bare username, all fields in one message) silently produced User: 0 in the confirm card (BUG-CRX-019) — cancelled, not confirmed. Retried with explicit numeric user ID (5), succeeded, then rejected with reason 'Insufficient team coverage during that period'. Verified on real /rf_leaves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>#3 luna.blossom (user 5), Unpaid, 2026-11-10 to 2026-11-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TC-CRX-095 (leave lifecycle — create/cancel)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Created (after 3 BUG-CRX-013 self-contradictions, 4th rephrasing succeeded) then cancelled via chat. Verified on real /rf_leaves.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name / ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Purpose / Used By (TC)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Last Verified</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Approved Hour Record</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>#1 — crux-qa (project 1), category 6 (Development - Quality Assurance &amp; Testing)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Active, 37.5h approved</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TC-CRX-104/105/106 (Budget Agent read surface, set cap, pending-check negative)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Created via chat, exact 37.5h, no rounding. Verified exactly on real /projects/crux-qa/settings/approved_hours_settings page. A second 10h proposal (TC-106) was correctly left unconfirmed and cancelled — total remains 37.5h.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name / ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Purpose / Used By (TC)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Last Verified</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Issue (fixture)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>#10 TC-CRX-109/110 Agile Board Fixture Card</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TC-CRX-109 (move card setup) — chat-based creation blocked by BUG-CRX-020</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Created via the real New Issue UI (Crux QA project) since Agile-chat issue creation is completely broken (BUG-CRX-020). Attempted move-to-'In Progress' via chat also failed the same way (fabricated confirm, no button, never moved).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name / ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Purpose / Used By (TC)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Last Verified</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>#1 Documentation (project crux-qa)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TC-CRX-134 (space/page create)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Created via chat after enabling the Redmineflux Knowledgebase module for crux-qa (real precondition gap, fixed via Settings &gt; Project UI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Node/Page</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>#1 Getting Started (space 1)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Published, v3 (3 versions total)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TC-CRX-134/135/136 (create, update, publish, unpublish, restore)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>v1: original grounded content. v2: deliberate 'DRAFT REVISION' test content. v3: restored from v1 (verified exact match). Currently published, showing v1's original content.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -930,12 +1655,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Renamed from ad-hoc 'crux_qa_manager' on 2026-09-14 per QA_CREDENTIALS.md Rule #1.</t>
+          <t>Renamed from ad-hoc 'crux_qa_manager' on 2026-09-14 per QA_CREDENTIALS.md Rule #1. 2026-09-16: reused as CRX-12 restricted-privilege test user (already fits: non-admin, crux-qa-only member, own Redmine API key already present under My account) -- no new user needed.</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1422,6 +2147,166 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>Created via chat confirm by luna.blossom. Frozen rule fr-7 blocks further status changes on this issue (still active).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TC-CRX-040 shared-key write test</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>crux-qa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CRX12 TC-CRX-040 (default CRUX_REQUIRE_USER_KEY=0, shared-key write proof)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Created via chat confirm by luna.blossom (shared service key).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC-CRX-039 admin-key write test</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>crux-qa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CRX12 TC-CRX-039 (admin key still works under CRUX_REQUIRE_USER_KEY=1)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Created via chat confirm by admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TC-CRX-041 per-user attribution test</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>crux-qa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CRX12 TC-CRX-041 (write attribution reflects real acting user, not shared service account)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Created via chat confirm by luna.blossom under CRUX_REQUIRE_USER_KEY=1. Author field confirmed = Crux Manager (luna.blossom), not admin/service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TC-CRX-042 toggle mid-session test</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>crux-qa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CRX12 TC-CRX-042 (toggling CRUX_REQUIRE_USER_KEY mid-session, exploratory)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Created via chat confirm by luna.blossom in session ses-022, after crux-core was recreated with CRUX_REQUIRE_USER_KEY flipped back to 0 mid-session; session survived the recreate.</t>
         </is>
       </c>
     </row>
@@ -1768,7 +2653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1961,6 +2846,51 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>Created via Sales Agent chat confirm (Crm Create Deal), linked to Contact Priya Sharma (ID:1). Stage stuck at Qualified — TC-CRX-087 stage-move attempts all failed (BUG-CRX-013), never advanced to Proposal. Related fixtures not yet tracked in this workbook (no Contacts/Companies/Leads sheet exists yet): Company "Acme Corp" (ID:1), Contact "Priya Sharma" (ID:1, priya.sharma@acmecorp.test, linked to Acme Corp), Lead "Rohan Verma" (ID:1, Nimbus Industries).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nimbus Industries Rollout</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>crux-qa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TC-CRX-089 (CRUX_AGENT_CRM_SALES.md) — lead-conversion-creates-deal evidence</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Created automatically via Crm Convert Lead (Lead #1 Rohan Verma -&gt; Contact #2 + Deal #4). Contact #2 "Rohan Verma" (rohan.verma@nimbusind.test) and Company #2 "Nimbus Industries" were also auto-created during this same conversion — no separate row tracked for them yet since this workbook has no Contacts/Companies sheet.</t>
         </is>
       </c>
     </row>
